--- a/nav_data/fund_data.xlsx
+++ b/nav_data/fund_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17820\Desktop\Private_nav_research\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17820\Desktop\Private_nav_research\nav_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74A9209E-0B06-4871-B113-0495C9DD4F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE340E5C-046B-4C4A-96F1-833E1E1E52C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="睿郡财富11号1期" sheetId="12" r:id="rId1"/>
@@ -1615,12 +1615,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="176" formatCode="0.00000"/>
     <numFmt numFmtId="177" formatCode="0.0000_);[Red]\(0.0000\)"/>
     <numFmt numFmtId="178" formatCode="[$-409]yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="179" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="180" formatCode="0.000_);[Red]\(0.000\)"/>
+    <numFmt numFmtId="183" formatCode="0.0000"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -1713,7 +1714,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1723,6 +1724,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1757,7 +1764,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1865,6 +1872,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4061,35 +4080,35 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="27">
+      <c r="A2" s="40">
         <v>42816</v>
       </c>
-      <c r="B2" s="28">
+      <c r="B2" s="39">
         <v>1</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
+      <c r="A3" s="40">
         <v>42818</v>
       </c>
-      <c r="B3" s="28">
+      <c r="B3" s="39">
         <v>1</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="27">
+      <c r="A4" s="40">
         <v>42825</v>
       </c>
-      <c r="B4" s="28">
+      <c r="B4" s="39">
         <v>1</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="39">
         <v>1</v>
       </c>
     </row>
@@ -9948,10 +9967,10 @@
       <c r="A2" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="38">
         <v>1</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="38">
         <v>1</v>
       </c>
     </row>
@@ -9959,10 +9978,10 @@
       <c r="A3" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -9970,10 +9989,10 @@
       <c r="A4" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -9981,10 +10000,10 @@
       <c r="A5" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -9992,10 +10011,10 @@
       <c r="A6" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -10003,10 +10022,10 @@
       <c r="A7" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -10014,10 +10033,10 @@
       <c r="A8" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="38">
         <v>1</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="38">
         <v>1</v>
       </c>
     </row>
@@ -10025,10 +10044,10 @@
       <c r="A9" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -10036,10 +10055,10 @@
       <c r="A10" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -10047,10 +10066,10 @@
       <c r="A11" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="38">
         <v>1.0001</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="38">
         <v>1.0001</v>
       </c>
     </row>
@@ -10058,10 +10077,10 @@
       <c r="A12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="37">
         <v>1.0003</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="37">
         <v>1.0003</v>
       </c>
     </row>
@@ -10069,10 +10088,10 @@
       <c r="A13" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="37">
         <v>1.0002</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="37">
         <v>1.0002</v>
       </c>
     </row>
